--- a/artfynd/A 17850-2021 artfynd.xlsx
+++ b/artfynd/A 17850-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129165311</v>
       </c>
       <c r="B2" t="n">
-        <v>97527</v>
+        <v>97530</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129165610</v>
       </c>
       <c r="B3" t="n">
-        <v>90555</v>
+        <v>90558</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129165551</v>
       </c>
       <c r="B4" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129166049</v>
       </c>
       <c r="B5" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129165267</v>
       </c>
       <c r="B6" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129165966</v>
       </c>
       <c r="B7" t="n">
-        <v>90905</v>
+        <v>90908</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 17850-2021 artfynd.xlsx
+++ b/artfynd/A 17850-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129165311</v>
       </c>
       <c r="B2" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129165610</v>
       </c>
       <c r="B3" t="n">
-        <v>90558</v>
+        <v>90562</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129165551</v>
       </c>
       <c r="B4" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129166049</v>
       </c>
       <c r="B5" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129165267</v>
       </c>
       <c r="B6" t="n">
-        <v>80169</v>
+        <v>80173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129165966</v>
       </c>
       <c r="B7" t="n">
-        <v>90908</v>
+        <v>90912</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 17850-2021 artfynd.xlsx
+++ b/artfynd/A 17850-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129165311</v>
       </c>
       <c r="B2" t="n">
-        <v>97540</v>
+        <v>97547</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129165610</v>
       </c>
       <c r="B3" t="n">
-        <v>90562</v>
+        <v>90569</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129165551</v>
       </c>
       <c r="B4" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129165966</v>
       </c>
       <c r="B7" t="n">
-        <v>90912</v>
+        <v>90919</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 17850-2021 artfynd.xlsx
+++ b/artfynd/A 17850-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129165311</v>
       </c>
       <c r="B2" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129165610</v>
       </c>
       <c r="B3" t="n">
-        <v>90569</v>
+        <v>90571</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129165551</v>
       </c>
       <c r="B4" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129166049</v>
       </c>
       <c r="B5" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129165267</v>
       </c>
       <c r="B6" t="n">
-        <v>80173</v>
+        <v>80175</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129165966</v>
       </c>
       <c r="B7" t="n">
-        <v>90919</v>
+        <v>90921</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
